--- a/OperaBale.xlsx
+++ b/OperaBale.xlsx
@@ -29,19 +29,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>Sezon yılı</t>
+    <t>sezon_yili</t>
   </si>
   <si>
-    <t>Opera ve bale salonu sayısı</t>
+    <t>opera_ve_bale_salonu_sayisi</t>
   </si>
   <si>
-    <t>Koltuk sayısı</t>
+    <t>koltuk_sayisi</t>
   </si>
   <si>
-    <t>Toplam oynanan eser sayısı</t>
+    <t>toplam_oynanan_eser_sayisi</t>
   </si>
   <si>
-    <t>Toplam seyirci sayısı</t>
+    <t>toplam_seyirci_sayisi</t>
   </si>
 </sst>
 </file>
